--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B2" t="n">
-        <v>94850</v>
+        <v>56584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R2" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>94850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>56584</v>
+        <v>94862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R2" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>94850</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>122425093</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -988,6 +988,326 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122478037</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79269</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>561116</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6517004</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122478022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94974</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561303</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6517126</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122478029</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94867</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561265</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6517031</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>94862</v>
+        <v>94867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425093</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>79269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,51 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561251</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517018</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +891,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R4" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478037</v>
+        <v>122478022</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>94974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,30 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561116</v>
+        <v>561303</v>
       </c>
       <c r="R5" t="n">
-        <v>6517004</v>
+        <v>6517126</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478022</v>
+        <v>122478029</v>
       </c>
       <c r="B6" t="n">
-        <v>94974</v>
+        <v>94867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561303</v>
+        <v>561265</v>
       </c>
       <c r="R6" t="n">
-        <v>6517126</v>
+        <v>6517031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>79269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,31 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R7" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>94867</v>
+        <v>94876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>2170</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +784,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424893</v>
+        <v>122425093</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>79270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,51 +891,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561157</v>
+        <v>561251</v>
       </c>
       <c r="R4" t="n">
-        <v>6517094</v>
+        <v>6517018</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +964,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +979,7 @@
         <v>122478022</v>
       </c>
       <c r="B5" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,11 +993,6 @@
       </c>
       <c r="E5" t="n">
         <v>2180</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1101,7 +1081,7 @@
         <v>122478029</v>
       </c>
       <c r="B6" t="n">
-        <v>94867</v>
+        <v>94876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,11 +1095,6 @@
       </c>
       <c r="E6" t="n">
         <v>2170</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1208,7 +1183,7 @@
         <v>122478037</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,11 +1197,6 @@
       </c>
       <c r="E7" t="n">
         <v>6453</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425001</v>
+        <v>122425093</v>
       </c>
       <c r="B2" t="n">
-        <v>94876</v>
+        <v>79274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>6453</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561221</v>
+        <v>561251</v>
       </c>
       <c r="R2" t="n">
-        <v>6517086</v>
+        <v>6517018</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>94889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,36 +891,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R4" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478022</v>
+        <v>122478037</v>
       </c>
       <c r="B5" t="n">
-        <v>94983</v>
+        <v>79274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -988,26 +1003,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1015,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561303</v>
+        <v>561116</v>
       </c>
       <c r="R5" t="n">
-        <v>6517126</v>
+        <v>6517004</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478029</v>
+        <v>122478022</v>
       </c>
       <c r="B6" t="n">
-        <v>94876</v>
+        <v>94996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1094,16 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561265</v>
+        <v>561303</v>
       </c>
       <c r="R6" t="n">
-        <v>6517031</v>
+        <v>6517126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478037</v>
+        <v>122478029</v>
       </c>
       <c r="B7" t="n">
-        <v>79270</v>
+        <v>94889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1192,25 +1216,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2170</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1218,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561116</v>
+        <v>561265</v>
       </c>
       <c r="R7" t="n">
-        <v>6517004</v>
+        <v>6517031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>94889</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>94902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,47 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R4" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>122478022</v>
       </c>
       <c r="B6" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>122478029</v>
       </c>
       <c r="B7" t="n">
-        <v>94889</v>
+        <v>94902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>94902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B4" t="n">
-        <v>94902</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,37 +895,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R4" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478037</v>
+        <v>122478022</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>95009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,30 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561116</v>
+        <v>561303</v>
       </c>
       <c r="R5" t="n">
-        <v>6517004</v>
+        <v>6517126</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478022</v>
+        <v>122478029</v>
       </c>
       <c r="B6" t="n">
-        <v>95009</v>
+        <v>94902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561303</v>
+        <v>561265</v>
       </c>
       <c r="R6" t="n">
-        <v>6517126</v>
+        <v>6517031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B7" t="n">
-        <v>94902</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,31 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R7" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425093</v>
+        <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>94904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561251</v>
+        <v>561221</v>
       </c>
       <c r="R2" t="n">
-        <v>6517018</v>
+        <v>6517086</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>94902</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424893</v>
+        <v>122425093</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,51 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561157</v>
+        <v>561251</v>
       </c>
       <c r="R4" t="n">
-        <v>6517094</v>
+        <v>6517018</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478022</v>
+        <v>122478029</v>
       </c>
       <c r="B5" t="n">
-        <v>95009</v>
+        <v>94904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561303</v>
+        <v>561265</v>
       </c>
       <c r="R5" t="n">
-        <v>6517126</v>
+        <v>6517031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B6" t="n">
-        <v>94902</v>
+        <v>79274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,31 +1110,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R6" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478037</v>
+        <v>122478022</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>95011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,30 +1216,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561116</v>
+        <v>561303</v>
       </c>
       <c r="R7" t="n">
-        <v>6517004</v>
+        <v>6517126</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425001</v>
+        <v>122425093</v>
       </c>
       <c r="B2" t="n">
-        <v>94904</v>
+        <v>79274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561221</v>
+        <v>561251</v>
       </c>
       <c r="R2" t="n">
-        <v>6517086</v>
+        <v>6517018</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>94904</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +891,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R4" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478029</v>
+        <v>122478022</v>
       </c>
       <c r="B5" t="n">
-        <v>94904</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561265</v>
+        <v>561303</v>
       </c>
       <c r="R5" t="n">
-        <v>6517031</v>
+        <v>6517126</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478037</v>
+        <v>122478029</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>94904</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,30 +1110,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561116</v>
+        <v>561265</v>
       </c>
       <c r="R6" t="n">
-        <v>6517004</v>
+        <v>6517031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478022</v>
+        <v>122478037</v>
       </c>
       <c r="B7" t="n">
-        <v>95011</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,31 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561303</v>
+        <v>561116</v>
       </c>
       <c r="R7" t="n">
-        <v>6517126</v>
+        <v>6517004</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>56594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R2" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425001</v>
+        <v>122425093</v>
       </c>
       <c r="B3" t="n">
-        <v>94904</v>
+        <v>79275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561221</v>
+        <v>561251</v>
       </c>
       <c r="R3" t="n">
-        <v>6517086</v>
+        <v>6517018</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>94905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,47 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R4" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478022</v>
+        <v>122478029</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>94905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561303</v>
+        <v>561265</v>
       </c>
       <c r="R5" t="n">
-        <v>6517126</v>
+        <v>6517031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478029</v>
+        <v>122478022</v>
       </c>
       <c r="B6" t="n">
-        <v>94904</v>
+        <v>95012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561265</v>
+        <v>561303</v>
       </c>
       <c r="R6" t="n">
-        <v>6517031</v>
+        <v>6517126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
         <v>122478037</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>56594</v>
+        <v>94908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R2" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>79275</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +789,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425001</v>
+        <v>122425093</v>
       </c>
       <c r="B4" t="n">
-        <v>94905</v>
+        <v>79278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561221</v>
+        <v>561251</v>
       </c>
       <c r="R4" t="n">
-        <v>6517086</v>
+        <v>6517018</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>122478029</v>
       </c>
       <c r="B5" t="n">
-        <v>94905</v>
+        <v>94908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478022</v>
+        <v>122478037</v>
       </c>
       <c r="B6" t="n">
-        <v>95012</v>
+        <v>79278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,31 +1110,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561303</v>
+        <v>561116</v>
       </c>
       <c r="R6" t="n">
-        <v>6517126</v>
+        <v>6517004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478037</v>
+        <v>122478022</v>
       </c>
       <c r="B7" t="n">
-        <v>79275</v>
+        <v>95015</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,30 +1216,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561116</v>
+        <v>561303</v>
       </c>
       <c r="R7" t="n">
-        <v>6517004</v>
+        <v>6517126</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425001</v>
+        <v>122425093</v>
       </c>
       <c r="B2" t="n">
-        <v>94908</v>
+        <v>79278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561221</v>
+        <v>561251</v>
       </c>
       <c r="R2" t="n">
-        <v>6517086</v>
+        <v>6517018</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>94908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425093</v>
+        <v>122424893</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +891,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561251</v>
+        <v>561157</v>
       </c>
       <c r="R4" t="n">
-        <v>6517018</v>
+        <v>6517094</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B5" t="n">
-        <v>94908</v>
+        <v>79278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,31 +1003,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R5" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478037</v>
+        <v>122478022</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>95015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,30 +1109,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561116</v>
+        <v>561303</v>
       </c>
       <c r="R6" t="n">
-        <v>6517004</v>
+        <v>6517126</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478022</v>
+        <v>122478029</v>
       </c>
       <c r="B7" t="n">
-        <v>95015</v>
+        <v>94908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561303</v>
+        <v>561265</v>
       </c>
       <c r="R7" t="n">
-        <v>6517126</v>
+        <v>6517031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122425093</v>
       </c>
       <c r="B2" t="n">
-        <v>79278</v>
+        <v>79380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122425001</v>
+        <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>94908</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561221</v>
+        <v>561157</v>
       </c>
       <c r="R3" t="n">
-        <v>6517086</v>
+        <v>6517094</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122424893</v>
+        <v>122425001</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,47 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561157</v>
+        <v>561221</v>
       </c>
       <c r="R4" t="n">
-        <v>6517094</v>
+        <v>6517086</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478037</v>
+        <v>122478029</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,30 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561116</v>
+        <v>561265</v>
       </c>
       <c r="R5" t="n">
-        <v>6517004</v>
+        <v>6517031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478022</v>
+        <v>122478037</v>
       </c>
       <c r="B6" t="n">
-        <v>95015</v>
+        <v>79380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,31 +1110,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561303</v>
+        <v>561116</v>
       </c>
       <c r="R6" t="n">
-        <v>6517126</v>
+        <v>6517004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478029</v>
+        <v>122478022</v>
       </c>
       <c r="B7" t="n">
-        <v>94908</v>
+        <v>95118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561265</v>
+        <v>561303</v>
       </c>
       <c r="R7" t="n">
-        <v>6517031</v>
+        <v>6517126</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,31 +1003,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1035,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R5" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478037</v>
+        <v>122478029</v>
       </c>
       <c r="B6" t="n">
-        <v>79380</v>
+        <v>95019</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,30 +1109,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561116</v>
+        <v>561265</v>
       </c>
       <c r="R6" t="n">
-        <v>6517004</v>
+        <v>6517031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>122478022</v>
       </c>
       <c r="B7" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478037</v>
+        <v>122478029</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>95021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,30 +1003,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1034,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561116</v>
+        <v>561265</v>
       </c>
       <c r="R5" t="n">
-        <v>6517004</v>
+        <v>6517031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478029</v>
+        <v>122478037</v>
       </c>
       <c r="B6" t="n">
-        <v>95019</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,31 +1110,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561265</v>
+        <v>561116</v>
       </c>
       <c r="R6" t="n">
-        <v>6517031</v>
+        <v>6517004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>122478022</v>
       </c>
       <c r="B7" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122424893</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122425093</v>
+        <v>122425001</v>
       </c>
       <c r="B2" t="n">
-        <v>79380</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561251</v>
+        <v>561221</v>
       </c>
       <c r="R2" t="n">
-        <v>6517018</v>
+        <v>6517086</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122424893</v>
+        <v>122478029</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,47 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561157</v>
+        <v>561265</v>
       </c>
       <c r="R3" t="n">
-        <v>6517094</v>
+        <v>6517031</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,33 +855,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122425001</v>
+        <v>122478022</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +885,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561221</v>
+        <v>561303</v>
       </c>
       <c r="R4" t="n">
-        <v>6517086</v>
+        <v>6517126</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,75 +957,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478029</v>
+        <v>122425093</v>
       </c>
       <c r="B5" t="n">
-        <v>95021</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561265</v>
+        <v>561251</v>
       </c>
       <c r="R5" t="n">
-        <v>6517031</v>
+        <v>6517018</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,19 +1055,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1101,12 +1076,7 @@
         <v>122478037</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,15 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478022</v>
+        <v>97569995</v>
       </c>
       <c r="B7" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,41 +1185,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561303</v>
+        <v>561193</v>
       </c>
       <c r="R7" t="n">
-        <v>6517126</v>
+        <v>6517145</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,12 +1246,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,22 +1260,232 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Kaj Almqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97569996</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klintaberget/Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561221</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6517184</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122424893</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Orrmossen, Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561157</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6517094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3617-2025 artfynd.xlsx
+++ b/artfynd/A 3617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122425001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122478029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122478022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122425093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122478037</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569996</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,8 +1526,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122424893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>